--- a/Assignment 5/Generator Design.xlsx
+++ b/Assignment 5/Generator Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arntzen/Desktop/FENT2321/Assignment 5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marku\Desktop\FENT2321\Assignment 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB578674-3D2E-E247-88F1-42027ACF035F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23D44ED-5888-487F-8E24-82E1BC77490D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DESIGN" sheetId="1" r:id="rId1"/>
@@ -707,9 +707,6 @@
     <t>Turbine RPM (=C11)</t>
   </si>
   <si>
-    <t>What-if Data Table analysis with different generator RPMS</t>
-  </si>
-  <si>
     <t>Turbine torque (=C12)</t>
   </si>
   <si>
@@ -735,6 +732,9 @@
   </si>
   <si>
     <t>75W at 1000RPM</t>
+  </si>
+  <si>
+    <t>What-if Data Table analysis with different generator RPMs</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1078,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1174,7 +1174,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1271,7 +1270,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1404,7 +1403,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>188.49555921538757</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1502,43 +1501,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>21.319664416245836</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>40.272426481720814</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>61.83966605811284</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>85.99059267646436</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>112.68260460098695</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>141.86178056201931</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>173.4634936595601</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>207.41313456715014</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>243.62692922149003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>282.01283471620826</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>322.47149615675687</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>364.89724678338041</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2769,97 +2768,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O111"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60.6640625" customWidth="1"/>
+    <col min="1" max="1" width="60.7109375" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="74.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="74.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="106" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="12" max="13" width="9.5" customWidth="1"/>
+    <col min="12" max="13" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="97" t="s">
+    <row r="1" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="64" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="63" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="65" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="96"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="64" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="97"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="66" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="96"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="65" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="66" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="67" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="68" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="62" t="s">
+      <c r="D8" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="E8" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="61" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:14" s="12" customFormat="1" ht="26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" s="12" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>12</v>
       </c>
@@ -2869,7 +2868,7 @@
       <c r="F9" s="13"/>
       <c r="G9" s="14"/>
     </row>
-    <row r="10" spans="1:14" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>1</v>
       </c>
@@ -2879,14 +2878,14 @@
       <c r="F10" s="18"/>
       <c r="G10" s="19"/>
     </row>
-    <row r="11" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="83">
+      <c r="C11" s="82">
         <v>1500</v>
       </c>
       <c r="D11" s="21" t="s">
@@ -2901,14 +2900,16 @@
       <c r="G11" s="22"/>
       <c r="H11" s="23"/>
     </row>
-    <row r="12" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="52"/>
+      <c r="C12" s="51">
+        <v>1.2</v>
+      </c>
       <c r="D12" s="21" t="s">
         <v>19</v>
       </c>
@@ -2921,14 +2922,14 @@
       <c r="G12" s="22"/>
       <c r="H12" s="23"/>
     </row>
-    <row r="13" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C13" s="16"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
       <c r="G13" s="14"/>
     </row>
-    <row r="14" spans="1:14" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>21</v>
       </c>
@@ -2937,16 +2938,16 @@
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="14"/>
-      <c r="N14" s="84"/>
-    </row>
-    <row r="15" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N14" s="83"/>
+    </row>
+    <row r="15" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="45">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="D15" s="13" t="s">
@@ -2959,16 +2960,16 @@
         <v>25</v>
       </c>
       <c r="G15" s="27"/>
-      <c r="N15" s="85"/>
-    </row>
-    <row r="16" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N15" s="84"/>
+    </row>
+    <row r="16" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="81">
+      <c r="C16" s="80">
         <v>0.01</v>
       </c>
       <c r="D16" s="13" t="s">
@@ -2981,14 +2982,14 @@
         <v>29</v>
       </c>
       <c r="G16" s="27"/>
-      <c r="N16" s="85"/>
-    </row>
-    <row r="17" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N16" s="84"/>
+    </row>
+    <row r="17" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="1:14" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>30</v>
       </c>
@@ -2997,14 +2998,16 @@
       <c r="E18" s="13"/>
       <c r="G18" s="14"/>
     </row>
-    <row r="19" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="49"/>
+      <c r="C19" s="48">
+        <v>2</v>
+      </c>
       <c r="D19" s="13" t="s">
         <v>33</v>
       </c>
@@ -3016,14 +3019,16 @@
       </c>
       <c r="G19" s="14"/>
     </row>
-    <row r="20" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>36</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="81"/>
+      <c r="C20" s="80">
+        <v>0.2</v>
+      </c>
       <c r="D20" s="13" t="s">
         <v>38</v>
       </c>
@@ -3034,15 +3039,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="13"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
-      <c r="M21" s="85"/>
-    </row>
-    <row r="22" spans="1:14" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="M21" s="84"/>
+    </row>
+    <row r="22" spans="1:14" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>41</v>
       </c>
@@ -3053,14 +3058,16 @@
       <c r="G22" s="14"/>
       <c r="N22" s="36"/>
     </row>
-    <row r="23" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>42</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="49"/>
+      <c r="C23" s="48">
+        <v>1</v>
+      </c>
       <c r="D23" s="13" t="s">
         <v>33</v>
       </c>
@@ -3071,38 +3078,42 @@
         <v>45</v>
       </c>
       <c r="G23" s="14"/>
-      <c r="M23" s="85"/>
+      <c r="M23" s="84"/>
       <c r="N23" s="36"/>
     </row>
-    <row r="24" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>46</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="50"/>
+      <c r="C24" s="49">
+        <v>1E-3</v>
+      </c>
       <c r="D24" s="13" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>48</v>
       </c>
       <c r="G24" s="14"/>
-      <c r="M24" s="85"/>
+      <c r="M24" s="84"/>
       <c r="N24" s="36"/>
     </row>
-    <row r="25" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="50"/>
+      <c r="C25" s="49">
+        <v>50</v>
+      </c>
       <c r="D25" s="13" t="s">
         <v>33</v>
       </c>
@@ -3114,17 +3125,17 @@
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
-      <c r="M25" s="85"/>
+      <c r="M25" s="84"/>
       <c r="N25" s="36"/>
     </row>
-    <row r="26" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>53</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="50">
+      <c r="C26" s="49">
         <v>0.1</v>
       </c>
       <c r="D26" s="13" t="s">
@@ -3138,17 +3149,19 @@
       </c>
       <c r="G26" s="27"/>
       <c r="H26" s="14"/>
-      <c r="M26" s="85"/>
+      <c r="M26" s="84"/>
       <c r="N26" s="36"/>
     </row>
-    <row r="27" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>56</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="80"/>
+      <c r="C27" s="79">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="D27" s="13"/>
       <c r="E27" s="26">
         <v>1.1000000000000001</v>
@@ -3157,17 +3170,19 @@
         <v>58</v>
       </c>
       <c r="G27" s="27"/>
-      <c r="M27" s="85"/>
+      <c r="M27" s="84"/>
       <c r="N27" s="36"/>
     </row>
-    <row r="28" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="50"/>
+      <c r="C28" s="49">
+        <v>0.9</v>
+      </c>
       <c r="D28" s="13" t="s">
         <v>33</v>
       </c>
@@ -3179,17 +3194,19 @@
       </c>
       <c r="G28" s="27"/>
       <c r="H28" s="14"/>
-      <c r="M28" s="85"/>
+      <c r="M28" s="84"/>
       <c r="N28" s="36"/>
     </row>
-    <row r="29" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>63</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C29" s="50"/>
+      <c r="C29" s="49">
+        <v>2</v>
+      </c>
       <c r="D29" s="13" t="s">
         <v>33</v>
       </c>
@@ -3201,17 +3218,19 @@
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="41"/>
-      <c r="M29" s="85"/>
+      <c r="M29" s="84"/>
       <c r="N29" s="36"/>
     </row>
-    <row r="30" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>67</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="82"/>
+      <c r="C30" s="81">
+        <v>30</v>
+      </c>
       <c r="D30" s="42" t="s">
         <v>69</v>
       </c>
@@ -3222,17 +3241,17 @@
         <v>71</v>
       </c>
       <c r="H30" s="14"/>
-      <c r="M30" s="85"/>
+      <c r="M30" s="84"/>
       <c r="N30" s="36"/>
     </row>
-    <row r="31" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
-      <c r="M31" s="85"/>
+      <c r="M31" s="84"/>
       <c r="N31" s="36"/>
     </row>
-    <row r="32" spans="1:14" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A32" s="17" t="s">
         <v>72</v>
       </c>
@@ -3242,17 +3261,17 @@
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
       <c r="H32" s="27"/>
-      <c r="M32" s="85"/>
+      <c r="M32" s="84"/>
       <c r="N32" s="36"/>
     </row>
-    <row r="33" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>73</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="46">
+      <c r="C33" s="45">
         <v>28</v>
       </c>
       <c r="D33" s="13" t="s">
@@ -3266,17 +3285,17 @@
       </c>
       <c r="G33" s="19"/>
       <c r="H33" s="22"/>
-      <c r="M33" s="85"/>
+      <c r="M33" s="84"/>
       <c r="N33" s="36"/>
     </row>
-    <row r="34" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>77</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="46">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="D34" s="13" t="s">
@@ -3287,17 +3306,17 @@
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="22"/>
-      <c r="M34" s="85"/>
+      <c r="M34" s="84"/>
       <c r="N34" s="36"/>
     </row>
-    <row r="35" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>81</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="46">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="D35" s="13" t="s">
@@ -3308,17 +3327,17 @@
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="M35" s="85"/>
+      <c r="M35" s="84"/>
       <c r="N35" s="36"/>
     </row>
-    <row r="36" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>83</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="46">
         <v>1000</v>
       </c>
       <c r="D36" s="13" t="s">
@@ -3331,21 +3350,21 @@
       <c r="G36" s="19"/>
       <c r="H36" s="14"/>
     </row>
-    <row r="37" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>86</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="46">
         <v>75</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>88</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F37" s="19" t="s">
         <v>89</v>
@@ -3353,14 +3372,14 @@
       <c r="G37" s="19"/>
       <c r="H37" s="14"/>
     </row>
-    <row r="38" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C38" s="71">
+      <c r="C38" s="70">
         <v>5</v>
       </c>
       <c r="D38" s="42" t="s">
@@ -3368,18 +3387,18 @@
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H38" s="14"/>
     </row>
-    <row r="39" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>92</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="71">
+      <c r="C39" s="70">
         <v>20</v>
       </c>
       <c r="D39" s="42" t="s">
@@ -3391,18 +3410,18 @@
       </c>
       <c r="H39" s="14"/>
     </row>
-    <row r="40" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>95</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="71">
+      <c r="C40" s="70">
         <f>3.9*10^(-3)</f>
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="D40" s="70" t="s">
+      <c r="D40" s="69" t="s">
         <v>97</v>
       </c>
       <c r="E40" s="13"/>
@@ -3411,18 +3430,18 @@
       </c>
       <c r="H40" s="14"/>
     </row>
-    <row r="41" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>99</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="48">
+      <c r="C41" s="47">
         <f>1.68*10^(-8)</f>
         <v>1.6799999999999998E-8</v>
       </c>
-      <c r="D41" s="70" t="s">
+      <c r="D41" s="69" t="s">
         <v>101</v>
       </c>
       <c r="E41" s="13"/>
@@ -3431,7 +3450,7 @@
       </c>
       <c r="H41" s="14"/>
     </row>
-    <row r="42" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="D42" s="20"/>
@@ -3440,7 +3459,7 @@
       <c r="G42" s="22"/>
       <c r="H42" s="23"/>
     </row>
-    <row r="43" spans="1:15" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" s="12" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A43" s="17" t="s">
         <v>103</v>
       </c>
@@ -3452,14 +3471,16 @@
       <c r="G43" s="22"/>
       <c r="H43" s="23"/>
     </row>
-    <row r="44" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
         <v>104</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C44" s="51"/>
+      <c r="C44" s="50">
+        <v>4</v>
+      </c>
       <c r="D44" s="13" t="s">
         <v>106</v>
       </c>
@@ -3471,7 +3492,7 @@
       </c>
       <c r="G44" s="24"/>
     </row>
-    <row r="45" spans="1:15" s="30" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" s="30" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="29"/>
       <c r="C45" s="29"/>
       <c r="D45" s="31"/>
@@ -3479,7 +3500,7 @@
       <c r="F45" s="32"/>
       <c r="G45" s="33"/>
     </row>
-    <row r="46" spans="1:15" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>109</v>
       </c>
@@ -3488,20 +3509,23 @@
       <c r="F46" s="10"/>
       <c r="G46" s="11"/>
     </row>
-    <row r="47" spans="1:15" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" s="12" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="34" t="s">
         <v>110</v>
       </c>
       <c r="D47" s="13"/>
     </row>
-    <row r="48" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
         <v>111</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C48" s="53"/>
+      <c r="C48" s="52">
+        <f>C27*(2*C26+2*2*PI()*(C15+C16/2)/C29)</f>
+        <v>0.56557519189487726</v>
+      </c>
       <c r="D48" s="13" t="s">
         <v>24</v>
       </c>
@@ -3521,14 +3545,17 @@
       <c r="N48" s="35"/>
       <c r="O48" s="35"/>
     </row>
-    <row r="49" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>115</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C49" s="54"/>
+      <c r="C49" s="53">
+        <f>C48*C25</f>
+        <v>28.278759594743864</v>
+      </c>
       <c r="D49" s="13" t="s">
         <v>24</v>
       </c>
@@ -3542,14 +3569,17 @@
       <c r="N49" s="35"/>
       <c r="O49" s="35"/>
     </row>
-    <row r="50" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>117</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C50" s="58"/>
+      <c r="C50" s="57">
+        <f>C49*C29*C23</f>
+        <v>56.557519189487728</v>
+      </c>
       <c r="D50" s="13" t="s">
         <v>24</v>
       </c>
@@ -3563,19 +3593,19 @@
       <c r="N50" s="35"/>
       <c r="O50" s="35"/>
     </row>
-    <row r="51" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C51" s="36"/>
       <c r="D51" s="13"/>
       <c r="E51" s="13"/>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="1:15" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" s="12" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A52" s="34" t="s">
         <v>119</v>
       </c>
       <c r="C52" s="36"/>
       <c r="D52" s="13"/>
-      <c r="E52" s="45"/>
+      <c r="E52" s="44"/>
       <c r="F52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="35"/>
@@ -3585,14 +3615,14 @@
       <c r="N52" s="35"/>
       <c r="O52" s="35"/>
     </row>
-    <row r="53" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>120</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="43">
+      <c r="C53" s="56">
         <v>1.1000000000000001</v>
       </c>
       <c r="D53" s="13"/>
@@ -3611,14 +3641,14 @@
       <c r="N53" s="35"/>
       <c r="O53" s="35"/>
     </row>
-    <row r="54" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>124</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C54" s="55"/>
+      <c r="C54" s="54"/>
       <c r="D54" s="13"/>
       <c r="E54" s="13" t="s">
         <v>126</v>
@@ -3636,14 +3666,17 @@
       <c r="N54" s="35"/>
       <c r="O54" s="35"/>
     </row>
-    <row r="55" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>128</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C55" s="75"/>
+      <c r="C55" s="74">
+        <f>PI()*((C24/2)^2)</f>
+        <v>7.8539816339744823E-7</v>
+      </c>
       <c r="D55" s="13" t="s">
         <v>130</v>
       </c>
@@ -3658,16 +3691,19 @@
       <c r="N55" s="35"/>
       <c r="O55" s="35"/>
     </row>
-    <row r="56" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" s="58">
+        <f>C41*(1+C40*(C30-C39))/C55</f>
+        <v>2.222465090126121E-2</v>
+      </c>
+      <c r="D56" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="C56" s="75"/>
-      <c r="D56" s="13" t="s">
-        <v>201</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="13"/>
@@ -3680,14 +3716,17 @@
       <c r="N56" s="35"/>
       <c r="O56" s="35"/>
     </row>
-    <row r="57" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>131</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C57" s="59"/>
+      <c r="C57" s="74">
+        <f>C56*C50*C53</f>
+        <v>1.3826682318105215</v>
+      </c>
       <c r="D57" s="13" t="s">
         <v>106</v>
       </c>
@@ -3701,44 +3740,50 @@
       <c r="N57" s="35"/>
       <c r="O57" s="35"/>
     </row>
-    <row r="58" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
         <v>133</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="75"/>
+      <c r="C58" s="74">
+        <f>C34*(C25/C33)^2*C29</f>
+        <v>5.1020408163265311E-3</v>
+      </c>
       <c r="D58" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E58" s="76"/>
+      <c r="E58" s="75"/>
       <c r="F58" s="26"/>
-      <c r="G58" s="79"/>
-    </row>
-    <row r="59" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G58" s="78"/>
+    </row>
+    <row r="59" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C59" s="54"/>
+      <c r="C59" s="53"/>
       <c r="D59" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="E59" s="45"/>
+      <c r="E59" s="44"/>
       <c r="F59" s="13"/>
       <c r="I59" s="13"/>
     </row>
-    <row r="60" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>138</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="77"/>
+      <c r="C60" s="76">
+        <f>C64*C58</f>
+        <v>0.80142669734433514</v>
+      </c>
       <c r="D60" s="13" t="s">
         <v>106</v>
       </c>
@@ -3746,13 +3791,13 @@
       <c r="F60" s="13"/>
       <c r="G60" s="37"/>
     </row>
-    <row r="61" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D61" s="13"/>
       <c r="E61" s="13"/>
       <c r="F61" s="13"/>
       <c r="G61" s="14"/>
     </row>
-    <row r="62" spans="1:15" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" s="12" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A62" s="34" t="s">
         <v>140</v>
       </c>
@@ -3761,14 +3806,14 @@
       <c r="F62" s="13"/>
       <c r="G62" s="27"/>
     </row>
-    <row r="63" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>141</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C63" s="57">
+      <c r="C63" s="56">
         <f>C11 * (PI() / 30)</f>
         <v>157.07963267948966</v>
       </c>
@@ -3787,14 +3832,17 @@
       <c r="N63" s="35"/>
       <c r="O63" s="35"/>
     </row>
-    <row r="64" spans="1:15" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
         <v>144</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="C64" s="56"/>
+      <c r="C64" s="55">
+        <f>C63*(C19/2)</f>
+        <v>157.07963267948966</v>
+      </c>
       <c r="D64" s="21" t="s">
         <v>143</v>
       </c>
@@ -3802,16 +3850,16 @@
       <c r="F64" s="20"/>
       <c r="G64" s="39"/>
     </row>
-    <row r="65" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>146</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="C65" s="55">
-        <f>((C15+C16/2)/1000)</f>
-        <v>4.9999999999999996E-5</v>
+      <c r="C65" s="54">
+        <f>C63*(C15+C16/2)</f>
+        <v>7.8539816339744828</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>148</v>
@@ -3826,14 +3874,17 @@
       <c r="N65" s="35"/>
       <c r="O65" s="35"/>
     </row>
-    <row r="66" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>149</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="C66" s="54"/>
+      <c r="C66" s="53">
+        <f>C25*C20*C65*(2*C26)*C29*C28/SQRT(2)</f>
+        <v>19.992973221712649</v>
+      </c>
       <c r="D66" s="13" t="s">
         <v>151</v>
       </c>
@@ -3841,14 +3892,17 @@
       <c r="F66" s="13"/>
       <c r="I66" s="14"/>
     </row>
-    <row r="67" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>152</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="55"/>
+      <c r="C67" s="54">
+        <f>C66/SQRT((C57+C44)^2+C60^2)</f>
+        <v>3.6738258691436783</v>
+      </c>
       <c r="D67" s="13" t="s">
         <v>154</v>
       </c>
@@ -3858,14 +3912,17 @@
       <c r="F67" s="26"/>
       <c r="I67" s="13"/>
     </row>
-    <row r="68" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>156</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C68" s="58"/>
+      <c r="C68" s="57">
+        <f>C67*C44</f>
+        <v>14.695303476574713</v>
+      </c>
       <c r="D68" s="13" t="s">
         <v>158</v>
       </c>
@@ -3873,34 +3930,40 @@
       <c r="F68" s="13"/>
       <c r="I68" s="13"/>
     </row>
-    <row r="69" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D69" s="13"/>
       <c r="E69" s="13"/>
       <c r="F69" s="13"/>
       <c r="G69" s="14"/>
     </row>
-    <row r="70" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>159</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C70" s="57"/>
+      <c r="C70" s="56">
+        <f>C68*C67</f>
+        <v>53.987986067157209</v>
+      </c>
       <c r="D70" s="13" t="s">
         <v>161</v>
       </c>
       <c r="E70" s="13"/>
       <c r="F70" s="13"/>
     </row>
-    <row r="71" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>162</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="C71" s="54"/>
+      <c r="C71" s="53">
+        <f>C23*C67^2*C57</f>
+        <v>18.66186830862183</v>
+      </c>
       <c r="D71" s="13" t="s">
         <v>161</v>
       </c>
@@ -3913,14 +3976,17 @@
       <c r="N71" s="35"/>
       <c r="O71" s="35"/>
     </row>
-    <row r="72" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
         <v>164</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C72" s="55"/>
+      <c r="C72" s="54">
+        <f>(C11/C36)*C37+C38</f>
+        <v>117.5</v>
+      </c>
       <c r="D72" s="13" t="s">
         <v>88</v>
       </c>
@@ -3928,14 +3994,17 @@
       <c r="F72" s="26"/>
       <c r="G72" s="16"/>
     </row>
-    <row r="73" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>166</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="C73" s="58"/>
+      <c r="C73" s="57">
+        <f>C70+C71+C72</f>
+        <v>190.14985437577906</v>
+      </c>
       <c r="D73" s="13" t="s">
         <v>161</v>
       </c>
@@ -3944,14 +4013,17 @@
       </c>
       <c r="F73" s="13"/>
     </row>
-    <row r="74" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
         <v>169</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C74" s="60"/>
+      <c r="C74" s="59">
+        <f>C70/C73</f>
+        <v>0.283923362678284</v>
+      </c>
       <c r="D74" s="13"/>
       <c r="E74" s="13" t="s">
         <v>171</v>
@@ -3959,21 +4031,24 @@
       <c r="F74" s="13"/>
       <c r="G74" s="37"/>
     </row>
-    <row r="75" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C75" s="36"/>
       <c r="D75" s="13"/>
       <c r="E75" s="13"/>
       <c r="F75" s="13"/>
       <c r="I75" s="13"/>
     </row>
-    <row r="76" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>172</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="C76" s="53"/>
+      <c r="C76" s="52">
+        <f>C73/C63</f>
+        <v>1.210531570084372</v>
+      </c>
       <c r="D76" s="13" t="s">
         <v>19</v>
       </c>
@@ -3988,23 +4063,23 @@
       <c r="N76" s="35"/>
       <c r="O76" s="35"/>
     </row>
-    <row r="77" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C77" s="78">
+      <c r="C77" s="77">
         <f>C12</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>19</v>
       </c>
       <c r="E77" s="13"/>
       <c r="F77" s="13"/>
-      <c r="G77" s="63" t="s">
+      <c r="G77" s="62" t="s">
         <v>174</v>
       </c>
       <c r="J77" s="35"/>
@@ -4014,21 +4089,21 @@
       <c r="N77" s="35"/>
       <c r="O77" s="35"/>
     </row>
-    <row r="78" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>175</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C78" s="72">
+      <c r="C78" s="71">
         <f>C76-C77</f>
-        <v>0</v>
+        <v>1.0531570084371999E-2</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E78" s="45" t="s">
+      <c r="E78" s="44" t="s">
         <v>177</v>
       </c>
       <c r="F78" s="13"/>
@@ -4042,20 +4117,20 @@
       <c r="N78" s="35"/>
       <c r="O78" s="35"/>
     </row>
-    <row r="79" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C79" s="38"/>
       <c r="D79" s="13"/>
       <c r="E79" s="13"/>
       <c r="F79" s="13"/>
     </row>
-    <row r="80" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C80" s="40"/>
       <c r="D80" s="13"/>
       <c r="E80" s="13"/>
       <c r="F80" s="13"/>
       <c r="G80" s="37"/>
     </row>
-    <row r="81" spans="1:15" s="12" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" s="12" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A81" s="34" t="s">
         <v>179</v>
       </c>
@@ -4065,16 +4140,16 @@
       <c r="F81" s="13"/>
       <c r="G81" s="37"/>
     </row>
-    <row r="82" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>180</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="C82" s="44" t="e">
-        <f>+C23*C83*C66*C66/((C57+C83)^2+C60^2)</f>
-        <v>#DIV/0!</v>
+      <c r="C82" s="43">
+        <f>+C23*C83*C66*C66/((C56+C83)^2+C60^2)</f>
+        <v>242.55986066862283</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>161</v>
@@ -4088,16 +4163,16 @@
         <v>183</v>
       </c>
     </row>
-    <row r="83" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
         <v>184</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C83" s="73">
-        <f>+SQRT(C57^2+C60^2)</f>
-        <v>0</v>
+      <c r="C83" s="72">
+        <f>+SQRT(C56^2+C60^2)</f>
+        <v>0.80173479799989433</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>106</v>
@@ -4117,16 +4192,16 @@
       <c r="N83" s="35"/>
       <c r="O83" s="35"/>
     </row>
-    <row r="84" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
         <v>188</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C84" s="74">
+      <c r="C84" s="73">
         <f>+C76/C63</f>
-        <v>0</v>
+        <v>7.7064833259088373E-3</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>190</v>
@@ -4140,14 +4215,14 @@
         <v>192</v>
       </c>
     </row>
-    <row r="85" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D85" s="13"/>
       <c r="E85" s="13"/>
       <c r="F85" s="13"/>
       <c r="G85" s="14"/>
     </row>
-    <row r="91" spans="1:15" s="12" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A91" s="86" t="s">
+    <row r="91" spans="1:15" s="12" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A91" s="85" t="s">
         <v>193</v>
       </c>
       <c r="D91" s="13"/>
@@ -4155,36 +4230,36 @@
       <c r="F91" s="13"/>
       <c r="G91" s="14"/>
     </row>
-    <row r="92" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D92" s="13"/>
       <c r="E92" s="13"/>
       <c r="F92" s="13"/>
       <c r="G92" s="14"/>
     </row>
-    <row r="93" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
         <v>194</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C93" s="94">
+      <c r="C93" s="93">
         <f>C12*C11/60*2*PI()</f>
-        <v>0</v>
+        <v>188.49555921538757</v>
       </c>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
       <c r="F93" s="13"/>
       <c r="G93" s="14"/>
     </row>
-    <row r="94" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
         <v>196</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C94" s="95">
+      <c r="C94" s="94">
         <f>C11</f>
         <v>1500</v>
       </c>
@@ -4193,202 +4268,202 @@
       <c r="F94" s="13"/>
       <c r="G94" s="14"/>
     </row>
-    <row r="95" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C95" s="85"/>
+    <row r="95" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C95" s="84"/>
       <c r="D95" s="13"/>
       <c r="E95" s="13"/>
       <c r="F95" s="13"/>
       <c r="G95" s="14"/>
     </row>
-    <row r="96" spans="1:15" s="12" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D96" s="13"/>
       <c r="E96" s="13"/>
       <c r="F96" s="13"/>
       <c r="G96" s="14"/>
     </row>
-    <row r="97" spans="1:7" s="12" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B97" s="96">
+        <v>206</v>
+      </c>
+      <c r="B97" s="95">
         <f>C11</f>
         <v>1500</v>
       </c>
-      <c r="C97" s="87">
+      <c r="C97" s="86">
         <f>C73</f>
-        <v>0</v>
+        <v>190.14985437577906</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E97" s="13"/>
       <c r="F97" s="13"/>
       <c r="G97" s="14"/>
     </row>
-    <row r="98" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="88">
+    <row r="98" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="87">
         <v>0</v>
       </c>
-      <c r="C98" s="89">
+      <c r="C98" s="88">
         <f t="dataTable" ref="C98:C110" dt2D="0" dtr="0" r1="C11"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D98" s="13"/>
       <c r="E98" s="13"/>
       <c r="F98" s="13"/>
       <c r="G98" s="14"/>
     </row>
-    <row r="99" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="90">
+    <row r="99" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="89">
         <v>200</v>
       </c>
-      <c r="C99" s="91">
-        <v>0</v>
+      <c r="C99" s="90">
+        <v>21.319664416245836</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
       <c r="F99" s="13"/>
       <c r="G99" s="14"/>
     </row>
-    <row r="100" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="90">
+    <row r="100" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="89">
         <v>400</v>
       </c>
-      <c r="C100" s="91">
-        <v>0</v>
+      <c r="C100" s="90">
+        <v>40.272426481720814</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
       <c r="F100" s="13"/>
       <c r="G100" s="14"/>
     </row>
-    <row r="101" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="90">
+    <row r="101" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="89">
         <v>600</v>
       </c>
-      <c r="C101" s="91">
-        <v>0</v>
+      <c r="C101" s="90">
+        <v>61.83966605811284</v>
       </c>
       <c r="D101" s="13"/>
       <c r="E101" s="13"/>
       <c r="F101" s="13"/>
       <c r="G101" s="14"/>
     </row>
-    <row r="102" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B102" s="90">
+    <row r="102" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="89">
         <v>800</v>
       </c>
-      <c r="C102" s="91">
-        <v>0</v>
+      <c r="C102" s="90">
+        <v>85.99059267646436</v>
       </c>
       <c r="D102" s="13"/>
       <c r="E102" s="13"/>
       <c r="F102" s="13"/>
       <c r="G102" s="14"/>
     </row>
-    <row r="103" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B103" s="90">
+    <row r="103" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="89">
         <v>1000</v>
       </c>
-      <c r="C103" s="91">
-        <v>0</v>
+      <c r="C103" s="90">
+        <v>112.68260460098695</v>
       </c>
       <c r="D103" s="13"/>
       <c r="E103" s="13"/>
       <c r="F103" s="13"/>
       <c r="G103" s="14"/>
     </row>
-    <row r="104" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="90">
+    <row r="104" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="89">
         <v>1200</v>
       </c>
-      <c r="C104" s="91">
-        <v>0</v>
+      <c r="C104" s="90">
+        <v>141.86178056201931</v>
       </c>
       <c r="D104" s="13"/>
       <c r="E104" s="13"/>
       <c r="F104" s="13"/>
       <c r="G104" s="14"/>
     </row>
-    <row r="105" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="90">
+    <row r="105" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="89">
         <v>1400</v>
       </c>
-      <c r="C105" s="91">
-        <v>0</v>
+      <c r="C105" s="90">
+        <v>173.4634936595601</v>
       </c>
       <c r="D105" s="13"/>
       <c r="E105" s="13"/>
       <c r="F105" s="13"/>
       <c r="G105" s="14"/>
     </row>
-    <row r="106" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="90">
+    <row r="106" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="89">
         <v>1600</v>
       </c>
-      <c r="C106" s="91">
-        <v>0</v>
+      <c r="C106" s="90">
+        <v>207.41313456715014</v>
       </c>
       <c r="D106" s="13"/>
       <c r="E106" s="13"/>
       <c r="F106" s="13"/>
       <c r="G106" s="14"/>
     </row>
-    <row r="107" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="90">
+    <row r="107" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="89">
         <v>1800</v>
       </c>
-      <c r="C107" s="91">
-        <v>0</v>
+      <c r="C107" s="90">
+        <v>243.62692922149003</v>
       </c>
       <c r="D107" s="13"/>
       <c r="E107" s="13"/>
       <c r="F107" s="13"/>
       <c r="G107" s="14"/>
     </row>
-    <row r="108" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="90">
+    <row r="108" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="89">
         <v>2000</v>
       </c>
-      <c r="C108" s="91">
-        <v>0</v>
+      <c r="C108" s="90">
+        <v>282.01283471620826</v>
       </c>
       <c r="D108" s="13"/>
       <c r="E108" s="13"/>
       <c r="F108" s="13"/>
       <c r="G108" s="14"/>
     </row>
-    <row r="109" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="90">
+    <row r="109" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="89">
         <v>2200</v>
       </c>
-      <c r="C109" s="91">
-        <v>0</v>
+      <c r="C109" s="90">
+        <v>322.47149615675687</v>
       </c>
       <c r="D109" s="13"/>
       <c r="E109" s="13"/>
       <c r="F109" s="13"/>
       <c r="G109" s="14"/>
     </row>
-    <row r="110" spans="1:7" s="12" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="92">
+    <row r="110" spans="1:7" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B110" s="91">
         <v>2400</v>
       </c>
-      <c r="C110" s="93">
-        <v>0</v>
+      <c r="C110" s="92">
+        <v>364.89724678338041</v>
       </c>
       <c r="D110" s="13"/>
       <c r="E110" s="13"/>
       <c r="F110" s="13"/>
       <c r="G110" s="14"/>
     </row>
-    <row r="111" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D111" s="13"/>
       <c r="E111" s="13"/>
       <c r="F111" s="13"/>
@@ -4416,15 +4491,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010094F1BE91CAA32A4FA328597B4EFE3ACE" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2aca6f94c8d86978e70ae67b520b84e8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="39c0dabe-6791-4282-927d-9f4490665562" xmlns:ns3="806083ee-ebb1-4caa-b9ed-1b2719206aaa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3da35c08f3c516271253674fd62704d4" ns2:_="" ns3:_="">
     <xsd:import namespace="39c0dabe-6791-4282-927d-9f4490665562"/>
@@ -4659,6 +4725,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC3A9434-1DD4-4E97-96EB-F40ECFBA7CA0}">
   <ds:schemaRefs>
@@ -4671,14 +4746,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4189B351-766F-4F69-B90B-B94C56907ECD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499D88EC-070D-4C20-A0B5-20CB874A3D7D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4695,4 +4762,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4189B351-766F-4F69-B90B-B94C56907ECD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Assignment 5/Generator Design.xlsx
+++ b/Assignment 5/Generator Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marku\Desktop\FENT2321\Assignment 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23D44ED-5888-487F-8E24-82E1BC77490D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C78D4F9-EA99-4ED9-AD6A-817F3061D577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DESIGN" sheetId="1" r:id="rId1"/>
@@ -1391,7 +1391,7 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1500</c:v>
+                  <c:v>1420</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1403,7 +1403,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>188.49555921538757</c:v>
+                  <c:v>178.44246272390023</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1504,40 +1504,40 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.319664416245836</c:v>
+                  <c:v>24.799456362740052</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>40.272426481720814</c:v>
+                  <c:v>54.179088652569462</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>61.83966605811284</c:v>
+                  <c:v>93.082869045764397</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>85.99059267646436</c:v>
+                  <c:v>141.41802309438884</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>112.68260460098695</c:v>
+                  <c:v>199.05592611376761</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>141.86178056201931</c:v>
+                  <c:v>265.83333546785207</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>173.4634936595601</c:v>
+                  <c:v>341.55393688040533</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>207.41313456715014</c:v>
+                  <c:v>425.99017773510013</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>243.62692922149003</c:v>
+                  <c:v>518.88535591339507</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>282.01283471620826</c:v>
+                  <c:v>619.95592915707709</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>322.47149615675687</c:v>
+                  <c:v>728.8940073010574</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>364.89724678338041</c:v>
+                  <c:v>845.36998803523727</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2886,7 +2886,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="82">
-        <v>1500</v>
+        <v>1420</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>14</v>
@@ -3136,7 +3136,8 @@
         <v>54</v>
       </c>
       <c r="C26" s="49">
-        <v>0.1</v>
+        <f>2*0.1</f>
+        <v>0.2</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>24</v>
@@ -3524,7 +3525,7 @@
       </c>
       <c r="C48" s="52">
         <f>C27*(2*C26+2*2*PI()*(C15+C16/2)/C29)</f>
-        <v>0.56557519189487726</v>
+        <v>0.78557519189487734</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>24</v>
@@ -3554,7 +3555,7 @@
       </c>
       <c r="C49" s="53">
         <f>C48*C25</f>
-        <v>28.278759594743864</v>
+        <v>39.278759594743867</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>24</v>
@@ -3578,7 +3579,7 @@
       </c>
       <c r="C50" s="57">
         <f>C49*C29*C23</f>
-        <v>56.557519189487728</v>
+        <v>78.557519189487735</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>24</v>
@@ -3725,7 +3726,7 @@
       </c>
       <c r="C57" s="74">
         <f>C56*C50*C53</f>
-        <v>1.3826682318105215</v>
+        <v>1.9205047836210429</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>106</v>
@@ -3782,7 +3783,7 @@
       </c>
       <c r="C60" s="76">
         <f>C64*C58</f>
-        <v>0.80142669734433514</v>
+        <v>0.75868394015263707</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>106</v>
@@ -3815,7 +3816,7 @@
       </c>
       <c r="C63" s="56">
         <f>C11 * (PI() / 30)</f>
-        <v>157.07963267948966</v>
+        <v>148.70205226991686</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>143</v>
@@ -3841,7 +3842,7 @@
       </c>
       <c r="C64" s="55">
         <f>C63*(C19/2)</f>
-        <v>157.07963267948966</v>
+        <v>148.70205226991686</v>
       </c>
       <c r="D64" s="21" t="s">
         <v>143</v>
@@ -3859,7 +3860,7 @@
       </c>
       <c r="C65" s="54">
         <f>C63*(C15+C16/2)</f>
-        <v>7.8539816339744828</v>
+        <v>7.4351026134958422</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>148</v>
@@ -3883,7 +3884,7 @@
       </c>
       <c r="C66" s="53">
         <f>C25*C20*C65*(2*C26)*C29*C28/SQRT(2)</f>
-        <v>19.992973221712649</v>
+        <v>37.853362633109271</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>151</v>
@@ -3901,7 +3902,7 @@
       </c>
       <c r="C67" s="54">
         <f>C66/SQRT((C57+C44)^2+C60^2)</f>
-        <v>3.6738258691436783</v>
+        <v>6.3417464760923776</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>154</v>
@@ -3921,7 +3922,7 @@
       </c>
       <c r="C68" s="57">
         <f>C67*C44</f>
-        <v>14.695303476574713</v>
+        <v>25.366985904369511</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>158</v>
@@ -3945,7 +3946,7 @@
       </c>
       <c r="C70" s="56">
         <f>C68*C67</f>
-        <v>53.987986067157209</v>
+        <v>160.87099346812036</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>161</v>
@@ -3962,7 +3963,7 @@
       </c>
       <c r="C71" s="53">
         <f>C23*C67^2*C57</f>
-        <v>18.66186830862183</v>
+        <v>77.238378125348675</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>161</v>
@@ -3985,7 +3986,7 @@
       </c>
       <c r="C72" s="54">
         <f>(C11/C36)*C37+C38</f>
-        <v>117.5</v>
+        <v>111.5</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>88</v>
@@ -4003,7 +4004,7 @@
       </c>
       <c r="C73" s="57">
         <f>C70+C71+C72</f>
-        <v>190.14985437577906</v>
+        <v>349.60937159346906</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>161</v>
@@ -4022,7 +4023,7 @@
       </c>
       <c r="C74" s="59">
         <f>C70/C73</f>
-        <v>0.283923362678284</v>
+        <v>0.46014496904042812</v>
       </c>
       <c r="D74" s="13"/>
       <c r="E74" s="13" t="s">
@@ -4047,7 +4048,7 @@
       </c>
       <c r="C76" s="52">
         <f>C73/C63</f>
-        <v>1.210531570084372</v>
+        <v>2.3510729425500787</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>19</v>
@@ -4098,7 +4099,7 @@
       </c>
       <c r="C78" s="71">
         <f>C76-C77</f>
-        <v>1.0531570084371999E-2</v>
+        <v>1.1510729425500787</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>19</v>
@@ -4149,7 +4150,7 @@
       </c>
       <c r="C82" s="43">
         <f>+C23*C83*C66*C66/((C56+C83)^2+C60^2)</f>
-        <v>242.55986066862283</v>
+        <v>917.06005188263828</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>161</v>
@@ -4172,7 +4173,7 @@
       </c>
       <c r="C83" s="72">
         <f>+SQRT(C56^2+C60^2)</f>
-        <v>0.80173479799989433</v>
+        <v>0.75900939134717771</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>106</v>
@@ -4201,7 +4202,7 @@
       </c>
       <c r="C84" s="73">
         <f>+C76/C63</f>
-        <v>7.7064833259088373E-3</v>
+        <v>1.5810628748300821E-2</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>190</v>
@@ -4245,7 +4246,7 @@
       </c>
       <c r="C93" s="93">
         <f>C12*C11/60*2*PI()</f>
-        <v>188.49555921538757</v>
+        <v>178.44246272390023</v>
       </c>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
@@ -4261,7 +4262,7 @@
       </c>
       <c r="C94" s="94">
         <f>C11</f>
-        <v>1500</v>
+        <v>1420</v>
       </c>
       <c r="D94" s="13"/>
       <c r="E94" s="13"/>
@@ -4293,11 +4294,11 @@
       </c>
       <c r="B97" s="95">
         <f>C11</f>
-        <v>1500</v>
+        <v>1420</v>
       </c>
       <c r="C97" s="86">
         <f>C73</f>
-        <v>190.14985437577906</v>
+        <v>349.60937159346906</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>203</v>
@@ -4324,7 +4325,7 @@
         <v>200</v>
       </c>
       <c r="C99" s="90">
-        <v>21.319664416245836</v>
+        <v>24.799456362740052</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
@@ -4336,7 +4337,7 @@
         <v>400</v>
       </c>
       <c r="C100" s="90">
-        <v>40.272426481720814</v>
+        <v>54.179088652569462</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
@@ -4348,7 +4349,7 @@
         <v>600</v>
       </c>
       <c r="C101" s="90">
-        <v>61.83966605811284</v>
+        <v>93.082869045764397</v>
       </c>
       <c r="D101" s="13"/>
       <c r="E101" s="13"/>
@@ -4360,7 +4361,7 @@
         <v>800</v>
       </c>
       <c r="C102" s="90">
-        <v>85.99059267646436</v>
+        <v>141.41802309438884</v>
       </c>
       <c r="D102" s="13"/>
       <c r="E102" s="13"/>
@@ -4372,7 +4373,7 @@
         <v>1000</v>
       </c>
       <c r="C103" s="90">
-        <v>112.68260460098695</v>
+        <v>199.05592611376761</v>
       </c>
       <c r="D103" s="13"/>
       <c r="E103" s="13"/>
@@ -4384,7 +4385,7 @@
         <v>1200</v>
       </c>
       <c r="C104" s="90">
-        <v>141.86178056201931</v>
+        <v>265.83333546785207</v>
       </c>
       <c r="D104" s="13"/>
       <c r="E104" s="13"/>
@@ -4396,7 +4397,7 @@
         <v>1400</v>
       </c>
       <c r="C105" s="90">
-        <v>173.4634936595601</v>
+        <v>341.55393688040533</v>
       </c>
       <c r="D105" s="13"/>
       <c r="E105" s="13"/>
@@ -4408,7 +4409,7 @@
         <v>1600</v>
       </c>
       <c r="C106" s="90">
-        <v>207.41313456715014</v>
+        <v>425.99017773510013</v>
       </c>
       <c r="D106" s="13"/>
       <c r="E106" s="13"/>
@@ -4420,7 +4421,7 @@
         <v>1800</v>
       </c>
       <c r="C107" s="90">
-        <v>243.62692922149003</v>
+        <v>518.88535591339507</v>
       </c>
       <c r="D107" s="13"/>
       <c r="E107" s="13"/>
@@ -4432,7 +4433,7 @@
         <v>2000</v>
       </c>
       <c r="C108" s="90">
-        <v>282.01283471620826</v>
+        <v>619.95592915707709</v>
       </c>
       <c r="D108" s="13"/>
       <c r="E108" s="13"/>
@@ -4444,7 +4445,7 @@
         <v>2200</v>
       </c>
       <c r="C109" s="90">
-        <v>322.47149615675687</v>
+        <v>728.8940073010574</v>
       </c>
       <c r="D109" s="13"/>
       <c r="E109" s="13"/>
@@ -4456,7 +4457,7 @@
         <v>2400</v>
       </c>
       <c r="C110" s="92">
-        <v>364.89724678338041</v>
+        <v>845.36998803523727</v>
       </c>
       <c r="D110" s="13"/>
       <c r="E110" s="13"/>
@@ -4491,6 +4492,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010094F1BE91CAA32A4FA328597B4EFE3ACE" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2aca6f94c8d86978e70ae67b520b84e8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="39c0dabe-6791-4282-927d-9f4490665562" xmlns:ns3="806083ee-ebb1-4caa-b9ed-1b2719206aaa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3da35c08f3c516271253674fd62704d4" ns2:_="" ns3:_="">
     <xsd:import namespace="39c0dabe-6791-4282-927d-9f4490665562"/>
@@ -4725,15 +4735,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC3A9434-1DD4-4E97-96EB-F40ECFBA7CA0}">
   <ds:schemaRefs>
@@ -4746,6 +4747,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4189B351-766F-4F69-B90B-B94C56907ECD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499D88EC-070D-4C20-A0B5-20CB874A3D7D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4762,12 +4771,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4189B351-766F-4F69-B90B-B94C56907ECD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Assignment 5/Generator Design.xlsx
+++ b/Assignment 5/Generator Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marku\Desktop\FENT2321\Assignment 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C78D4F9-EA99-4ED9-AD6A-817F3061D577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC48352B-89BC-499F-B19C-AC17A3A3D739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DESIGN" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="208">
   <si>
     <t>Generator design sheet</t>
   </si>
@@ -735,6 +735,9 @@
   </si>
   <si>
     <t>What-if Data Table analysis with different generator RPMs</t>
+  </si>
+  <si>
+    <t>d ..</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1394,7 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1420</c:v>
+                  <c:v>2483</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1403,7 +1406,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>178.44246272390023</c:v>
+                  <c:v>312.02298235453821</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1504,40 +1507,40 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.799456362740052</c:v>
+                  <c:v>46.84635833146362</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.179088652569462</c:v>
+                  <c:v>123.8611935350005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>93.082869045764397</c:v>
+                  <c:v>205.29093342270255</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>141.41802309438884</c:v>
+                  <c:v>275.32118086437083</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>199.05592611376761</c:v>
+                  <c:v>331.58700699023609</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>265.83333546785207</c:v>
+                  <c:v>376.59988656031845</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>341.55393688040533</c:v>
+                  <c:v>413.42548213414159</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>425.99017773510013</c:v>
+                  <c:v>444.4975436146517</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>518.88535591339507</c:v>
+                  <c:v>471.53738499953806</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>619.95592915707709</c:v>
+                  <c:v>495.7215026372478</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>728.8940073010574</c:v>
+                  <c:v>517.85107736491</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>845.36998803523727</c:v>
+                  <c:v>538.47670431146423</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2886,7 +2889,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="82">
-        <v>1420</v>
+        <v>2483</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>14</v>
@@ -2970,7 +2973,7 @@
         <v>27</v>
       </c>
       <c r="C16" s="80">
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>24</v>
@@ -3006,7 +3009,7 @@
         <v>32</v>
       </c>
       <c r="C19" s="48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>33</v>
@@ -3041,7 +3044,9 @@
     </row>
     <row r="21" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
-      <c r="C21" s="16"/>
+      <c r="C21" s="16" t="s">
+        <v>207</v>
+      </c>
       <c r="D21" s="13"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
@@ -3089,7 +3094,7 @@
         <v>47</v>
       </c>
       <c r="C24" s="49">
-        <v>1E-3</v>
+        <v>1.1800000000000001E-3</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>24</v>
@@ -3136,8 +3141,7 @@
         <v>54</v>
       </c>
       <c r="C26" s="49">
-        <f>2*0.1</f>
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>24</v>
@@ -3206,7 +3210,7 @@
         <v>64</v>
       </c>
       <c r="C29" s="49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>33</v>
@@ -3480,7 +3484,7 @@
         <v>105</v>
       </c>
       <c r="C44" s="50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>106</v>
@@ -3525,7 +3529,7 @@
       </c>
       <c r="C48" s="52">
         <f>C27*(2*C26+2*2*PI()*(C15+C16/2)/C29)</f>
-        <v>0.78557519189487734</v>
+        <v>0.44542697574481055</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>24</v>
@@ -3555,7 +3559,7 @@
       </c>
       <c r="C49" s="53">
         <f>C48*C25</f>
-        <v>39.278759594743867</v>
+        <v>22.271348787240527</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>24</v>
@@ -3579,7 +3583,7 @@
       </c>
       <c r="C50" s="57">
         <f>C49*C29*C23</f>
-        <v>78.557519189487735</v>
+        <v>89.085395148962107</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>24</v>
@@ -3676,7 +3680,7 @@
       </c>
       <c r="C55" s="74">
         <f>PI()*((C24/2)^2)</f>
-        <v>7.8539816339744823E-7</v>
+        <v>1.0935884027146072E-6</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>130</v>
@@ -3701,7 +3705,7 @@
       </c>
       <c r="C56" s="58">
         <f>C41*(1+C40*(C30-C39))/C55</f>
-        <v>2.222465090126121E-2</v>
+        <v>1.5961398234172079E-2</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>200</v>
@@ -3726,7 +3730,7 @@
       </c>
       <c r="C57" s="74">
         <f>C56*C50*C53</f>
-        <v>1.9205047836210429</v>
+        <v>1.5641202157032823</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>106</v>
@@ -3750,7 +3754,7 @@
       </c>
       <c r="C58" s="74">
         <f>C34*(C25/C33)^2*C29</f>
-        <v>5.1020408163265311E-3</v>
+        <v>1.0204081632653062E-2</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>79</v>
@@ -3783,7 +3787,7 @@
       </c>
       <c r="C60" s="76">
         <f>C64*C58</f>
-        <v>0.75868394015263707</v>
+        <v>5.3065133053492897</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>106</v>
@@ -3816,7 +3820,7 @@
       </c>
       <c r="C63" s="56">
         <f>C11 * (PI() / 30)</f>
-        <v>148.70205226991686</v>
+        <v>260.01915196211519</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>143</v>
@@ -3842,7 +3846,7 @@
       </c>
       <c r="C64" s="55">
         <f>C63*(C19/2)</f>
-        <v>148.70205226991686</v>
+        <v>520.03830392423038</v>
       </c>
       <c r="D64" s="21" t="s">
         <v>143</v>
@@ -3860,7 +3864,7 @@
       </c>
       <c r="C65" s="54">
         <f>C63*(C15+C16/2)</f>
-        <v>7.4351026134958422</v>
+        <v>13.651005478011047</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>148</v>
@@ -3884,7 +3888,7 @@
       </c>
       <c r="C66" s="53">
         <f>C25*C20*C65*(2*C26)*C29*C28/SQRT(2)</f>
-        <v>37.853362633109271</v>
+        <v>83.39948821598098</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>151</v>
@@ -3902,7 +3906,7 @@
       </c>
       <c r="C67" s="54">
         <f>C66/SQRT((C57+C44)^2+C60^2)</f>
-        <v>6.3417464760923776</v>
+        <v>15.075205891272338</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>154</v>
@@ -3922,7 +3926,7 @@
       </c>
       <c r="C68" s="57">
         <f>C67*C44</f>
-        <v>25.366985904369511</v>
+        <v>0</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>158</v>
@@ -3946,7 +3950,7 @@
       </c>
       <c r="C70" s="56">
         <f>C68*C67</f>
-        <v>160.87099346812036</v>
+        <v>0</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>161</v>
@@ -3963,7 +3967,7 @@
       </c>
       <c r="C71" s="53">
         <f>C23*C67^2*C57</f>
-        <v>77.238378125348675</v>
+        <v>355.46482672793343</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>161</v>
@@ -3986,7 +3990,7 @@
       </c>
       <c r="C72" s="54">
         <f>(C11/C36)*C37+C38</f>
-        <v>111.5</v>
+        <v>191.22499999999999</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>88</v>
@@ -4004,7 +4008,7 @@
       </c>
       <c r="C73" s="57">
         <f>C70+C71+C72</f>
-        <v>349.60937159346906</v>
+        <v>546.68982672793345</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>161</v>
@@ -4023,7 +4027,7 @@
       </c>
       <c r="C74" s="59">
         <f>C70/C73</f>
-        <v>0.46014496904042812</v>
+        <v>0</v>
       </c>
       <c r="D74" s="13"/>
       <c r="E74" s="13" t="s">
@@ -4048,7 +4052,7 @@
       </c>
       <c r="C76" s="52">
         <f>C73/C63</f>
-        <v>2.3510729425500787</v>
+        <v>2.1024983067692884</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>19</v>
@@ -4099,7 +4103,7 @@
       </c>
       <c r="C78" s="71">
         <f>C76-C77</f>
-        <v>1.1510729425500787</v>
+        <v>0.90249830676928844</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>19</v>
@@ -4150,7 +4154,7 @@
       </c>
       <c r="C82" s="43">
         <f>+C23*C83*C66*C66/((C56+C83)^2+C60^2)</f>
-        <v>917.06005188263828</v>
+        <v>653.40313032639608</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>161</v>
@@ -4173,7 +4177,7 @@
       </c>
       <c r="C83" s="72">
         <f>+SQRT(C56^2+C60^2)</f>
-        <v>0.75900939134717771</v>
+        <v>5.3065373103449138</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>106</v>
@@ -4202,7 +4206,7 @@
       </c>
       <c r="C84" s="73">
         <f>+C76/C63</f>
-        <v>1.5810628748300821E-2</v>
+        <v>8.085936327781049E-3</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>190</v>
@@ -4246,7 +4250,7 @@
       </c>
       <c r="C93" s="93">
         <f>C12*C11/60*2*PI()</f>
-        <v>178.44246272390023</v>
+        <v>312.02298235453821</v>
       </c>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
@@ -4262,7 +4266,7 @@
       </c>
       <c r="C94" s="94">
         <f>C11</f>
-        <v>1420</v>
+        <v>2483</v>
       </c>
       <c r="D94" s="13"/>
       <c r="E94" s="13"/>
@@ -4294,11 +4298,11 @@
       </c>
       <c r="B97" s="95">
         <f>C11</f>
-        <v>1420</v>
+        <v>2483</v>
       </c>
       <c r="C97" s="86">
         <f>C73</f>
-        <v>349.60937159346906</v>
+        <v>546.68982672793345</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>203</v>
@@ -4325,7 +4329,7 @@
         <v>200</v>
       </c>
       <c r="C99" s="90">
-        <v>24.799456362740052</v>
+        <v>46.84635833146362</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
@@ -4337,7 +4341,7 @@
         <v>400</v>
       </c>
       <c r="C100" s="90">
-        <v>54.179088652569462</v>
+        <v>123.8611935350005</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
@@ -4349,7 +4353,7 @@
         <v>600</v>
       </c>
       <c r="C101" s="90">
-        <v>93.082869045764397</v>
+        <v>205.29093342270255</v>
       </c>
       <c r="D101" s="13"/>
       <c r="E101" s="13"/>
@@ -4361,7 +4365,7 @@
         <v>800</v>
       </c>
       <c r="C102" s="90">
-        <v>141.41802309438884</v>
+        <v>275.32118086437083</v>
       </c>
       <c r="D102" s="13"/>
       <c r="E102" s="13"/>
@@ -4373,7 +4377,7 @@
         <v>1000</v>
       </c>
       <c r="C103" s="90">
-        <v>199.05592611376761</v>
+        <v>331.58700699023609</v>
       </c>
       <c r="D103" s="13"/>
       <c r="E103" s="13"/>
@@ -4385,7 +4389,7 @@
         <v>1200</v>
       </c>
       <c r="C104" s="90">
-        <v>265.83333546785207</v>
+        <v>376.59988656031845</v>
       </c>
       <c r="D104" s="13"/>
       <c r="E104" s="13"/>
@@ -4397,7 +4401,7 @@
         <v>1400</v>
       </c>
       <c r="C105" s="90">
-        <v>341.55393688040533</v>
+        <v>413.42548213414159</v>
       </c>
       <c r="D105" s="13"/>
       <c r="E105" s="13"/>
@@ -4409,7 +4413,7 @@
         <v>1600</v>
       </c>
       <c r="C106" s="90">
-        <v>425.99017773510013</v>
+        <v>444.4975436146517</v>
       </c>
       <c r="D106" s="13"/>
       <c r="E106" s="13"/>
@@ -4421,7 +4425,7 @@
         <v>1800</v>
       </c>
       <c r="C107" s="90">
-        <v>518.88535591339507</v>
+        <v>471.53738499953806</v>
       </c>
       <c r="D107" s="13"/>
       <c r="E107" s="13"/>
@@ -4433,7 +4437,7 @@
         <v>2000</v>
       </c>
       <c r="C108" s="90">
-        <v>619.95592915707709</v>
+        <v>495.7215026372478</v>
       </c>
       <c r="D108" s="13"/>
       <c r="E108" s="13"/>
@@ -4445,7 +4449,7 @@
         <v>2200</v>
       </c>
       <c r="C109" s="90">
-        <v>728.8940073010574</v>
+        <v>517.85107736491</v>
       </c>
       <c r="D109" s="13"/>
       <c r="E109" s="13"/>
@@ -4457,7 +4461,7 @@
         <v>2400</v>
       </c>
       <c r="C110" s="92">
-        <v>845.36998803523727</v>
+        <v>538.47670431146423</v>
       </c>
       <c r="D110" s="13"/>
       <c r="E110" s="13"/>
@@ -4492,15 +4496,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010094F1BE91CAA32A4FA328597B4EFE3ACE" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2aca6f94c8d86978e70ae67b520b84e8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="39c0dabe-6791-4282-927d-9f4490665562" xmlns:ns3="806083ee-ebb1-4caa-b9ed-1b2719206aaa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3da35c08f3c516271253674fd62704d4" ns2:_="" ns3:_="">
     <xsd:import namespace="39c0dabe-6791-4282-927d-9f4490665562"/>
@@ -4735,6 +4730,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC3A9434-1DD4-4E97-96EB-F40ECFBA7CA0}">
   <ds:schemaRefs>
@@ -4747,14 +4751,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4189B351-766F-4F69-B90B-B94C56907ECD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499D88EC-070D-4C20-A0B5-20CB874A3D7D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4771,4 +4767,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4189B351-766F-4F69-B90B-B94C56907ECD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Assignment 5/Generator Design.xlsx
+++ b/Assignment 5/Generator Design.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marku\Desktop\FENT2321\Assignment 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC48352B-89BC-499F-B19C-AC17A3A3D739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A05E60-82E8-47D3-8D3F-A27111AF7B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DESIGN" sheetId="1" r:id="rId1"/>
@@ -1394,7 +1394,7 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2483</c:v>
+                  <c:v>1579</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1406,7 +1406,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>312.02298235453821</c:v>
+                  <c:v>301.43759534777769</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1507,40 +1507,40 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46.84635833146362</c:v>
+                  <c:v>22.889242788734624</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123.8611935350005</c:v>
+                  <c:v>46.550482282864735</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>205.29093342270255</c:v>
+                  <c:v>75.964288265062493</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>275.32118086437083</c:v>
+                  <c:v>111.09839798879378</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>331.58700699023609</c:v>
+                  <c:v>151.90789627600935</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>376.59988656031845</c:v>
+                  <c:v>198.3354650250912</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>413.42548213414159</c:v>
+                  <c:v>250.31169955294243</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>444.4975436146517</c:v>
+                  <c:v>307.7554885329298</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>471.53738499953806</c:v>
+                  <c:v>370.57445368112303</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>495.7215026372478</c:v>
+                  <c:v>438.66544479602601</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>517.85107736491</c:v>
+                  <c:v>511.91508527943597</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>538.47670431146423</c:v>
+                  <c:v>590.20036286422874</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2770,6 +2770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:O111"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2889,7 +2890,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="82">
-        <v>2483</v>
+        <v>1579</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>14</v>
@@ -2911,7 +2912,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="51">
-        <v>1.2</v>
+        <v>1.823</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>19</v>
@@ -3009,7 +3010,7 @@
         <v>32</v>
       </c>
       <c r="C19" s="48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>33</v>
@@ -3117,7 +3118,7 @@
         <v>50</v>
       </c>
       <c r="C25" s="49">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>33</v>
@@ -3484,7 +3485,7 @@
         <v>105</v>
       </c>
       <c r="C44" s="50">
-        <v>0</v>
+        <v>20.61</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>106</v>
@@ -3559,7 +3560,7 @@
       </c>
       <c r="C49" s="53">
         <f>C48*C25</f>
-        <v>22.271348787240527</v>
+        <v>26.725618544688633</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>24</v>
@@ -3583,7 +3584,7 @@
       </c>
       <c r="C50" s="57">
         <f>C49*C29*C23</f>
-        <v>89.085395148962107</v>
+        <v>106.90247417875453</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>24</v>
@@ -3730,7 +3731,7 @@
       </c>
       <c r="C57" s="74">
         <f>C56*C50*C53</f>
-        <v>1.5641202157032823</v>
+        <v>1.8769442588439389</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>106</v>
@@ -3754,7 +3755,7 @@
       </c>
       <c r="C58" s="74">
         <f>C34*(C25/C33)^2*C29</f>
-        <v>1.0204081632653062E-2</v>
+        <v>1.4693877551020407E-2</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>79</v>
@@ -3787,7 +3788,7 @@
       </c>
       <c r="C60" s="76">
         <f>C64*C58</f>
-        <v>5.3065133053492897</v>
+        <v>2.4296692898048731</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>106</v>
@@ -3820,7 +3821,7 @@
       </c>
       <c r="C63" s="56">
         <f>C11 * (PI() / 30)</f>
-        <v>260.01915196211519</v>
+        <v>165.35249333394276</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>143</v>
@@ -3846,7 +3847,7 @@
       </c>
       <c r="C64" s="55">
         <f>C63*(C19/2)</f>
-        <v>520.03830392423038</v>
+        <v>165.35249333394276</v>
       </c>
       <c r="D64" s="21" t="s">
         <v>143</v>
@@ -3864,7 +3865,7 @@
       </c>
       <c r="C65" s="54">
         <f>C63*(C15+C16/2)</f>
-        <v>13.651005478011047</v>
+        <v>8.6810059000319946</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>148</v>
@@ -3888,7 +3889,7 @@
       </c>
       <c r="C66" s="53">
         <f>C25*C20*C65*(2*C26)*C29*C28/SQRT(2)</f>
-        <v>83.39948821598098</v>
+        <v>63.642911909641875</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>151</v>
@@ -3906,7 +3907,7 @@
       </c>
       <c r="C67" s="54">
         <f>C66/SQRT((C57+C44)^2+C60^2)</f>
-        <v>15.075205891272338</v>
+        <v>2.813838872318625</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>154</v>
@@ -3926,7 +3927,7 @@
       </c>
       <c r="C68" s="57">
         <f>C67*C44</f>
-        <v>0</v>
+        <v>57.993219158486859</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>158</v>
@@ -3950,7 +3951,7 @@
       </c>
       <c r="C70" s="56">
         <f>C68*C67</f>
-        <v>0</v>
+        <v>163.18357439904355</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>161</v>
@@ -3967,7 +3968,7 @@
       </c>
       <c r="C71" s="53">
         <f>C23*C67^2*C57</f>
-        <v>355.46482672793343</v>
+        <v>14.86106128607072</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>161</v>
@@ -3990,7 +3991,7 @@
       </c>
       <c r="C72" s="54">
         <f>(C11/C36)*C37+C38</f>
-        <v>191.22499999999999</v>
+        <v>123.425</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>88</v>
@@ -4008,7 +4009,7 @@
       </c>
       <c r="C73" s="57">
         <f>C70+C71+C72</f>
-        <v>546.68982672793345</v>
+        <v>301.46963568511427</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>161</v>
@@ -4027,7 +4028,7 @@
       </c>
       <c r="C74" s="59">
         <f>C70/C73</f>
-        <v>0</v>
+        <v>0.54129356685689289</v>
       </c>
       <c r="D74" s="13"/>
       <c r="E74" s="13" t="s">
@@ -4052,7 +4053,7 @@
       </c>
       <c r="C76" s="52">
         <f>C73/C63</f>
-        <v>2.1024983067692884</v>
+        <v>1.8231937699074903</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>19</v>
@@ -4077,7 +4078,7 @@
       </c>
       <c r="C77" s="77">
         <f>C12</f>
-        <v>1.2</v>
+        <v>1.823</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>19</v>
@@ -4103,7 +4104,7 @@
       </c>
       <c r="C78" s="71">
         <f>C76-C77</f>
-        <v>0.90249830676928844</v>
+        <v>1.9376990749031542E-4</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>19</v>
@@ -4154,7 +4155,7 @@
       </c>
       <c r="C82" s="43">
         <f>+C23*C83*C66*C66/((C56+C83)^2+C60^2)</f>
-        <v>653.40313032639608</v>
+        <v>828.07543839778043</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>161</v>
@@ -4177,7 +4178,7 @@
       </c>
       <c r="C83" s="72">
         <f>+SQRT(C56^2+C60^2)</f>
-        <v>5.3065373103449138</v>
+        <v>2.4297217174101453</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>106</v>
@@ -4206,7 +4207,7 @@
       </c>
       <c r="C84" s="73">
         <f>+C76/C63</f>
-        <v>8.085936327781049E-3</v>
+        <v>1.1026103889618421E-2</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>190</v>
@@ -4250,7 +4251,7 @@
       </c>
       <c r="C93" s="93">
         <f>C12*C11/60*2*PI()</f>
-        <v>312.02298235453821</v>
+        <v>301.43759534777769</v>
       </c>
       <c r="D93" s="13"/>
       <c r="E93" s="13"/>
@@ -4266,7 +4267,7 @@
       </c>
       <c r="C94" s="94">
         <f>C11</f>
-        <v>2483</v>
+        <v>1579</v>
       </c>
       <c r="D94" s="13"/>
       <c r="E94" s="13"/>
@@ -4298,11 +4299,11 @@
       </c>
       <c r="B97" s="95">
         <f>C11</f>
-        <v>2483</v>
+        <v>1579</v>
       </c>
       <c r="C97" s="86">
         <f>C73</f>
-        <v>546.68982672793345</v>
+        <v>301.46963568511427</v>
       </c>
       <c r="D97" s="14" t="s">
         <v>203</v>
@@ -4329,7 +4330,7 @@
         <v>200</v>
       </c>
       <c r="C99" s="90">
-        <v>46.84635833146362</v>
+        <v>22.889242788734624</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
@@ -4341,7 +4342,7 @@
         <v>400</v>
       </c>
       <c r="C100" s="90">
-        <v>123.8611935350005</v>
+        <v>46.550482282864735</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="13"/>
@@ -4353,7 +4354,7 @@
         <v>600</v>
       </c>
       <c r="C101" s="90">
-        <v>205.29093342270255</v>
+        <v>75.964288265062493</v>
       </c>
       <c r="D101" s="13"/>
       <c r="E101" s="13"/>
@@ -4365,7 +4366,7 @@
         <v>800</v>
       </c>
       <c r="C102" s="90">
-        <v>275.32118086437083</v>
+        <v>111.09839798879378</v>
       </c>
       <c r="D102" s="13"/>
       <c r="E102" s="13"/>
@@ -4377,7 +4378,7 @@
         <v>1000</v>
       </c>
       <c r="C103" s="90">
-        <v>331.58700699023609</v>
+        <v>151.90789627600935</v>
       </c>
       <c r="D103" s="13"/>
       <c r="E103" s="13"/>
@@ -4389,7 +4390,7 @@
         <v>1200</v>
       </c>
       <c r="C104" s="90">
-        <v>376.59988656031845</v>
+        <v>198.3354650250912</v>
       </c>
       <c r="D104" s="13"/>
       <c r="E104" s="13"/>
@@ -4401,7 +4402,7 @@
         <v>1400</v>
       </c>
       <c r="C105" s="90">
-        <v>413.42548213414159</v>
+        <v>250.31169955294243</v>
       </c>
       <c r="D105" s="13"/>
       <c r="E105" s="13"/>
@@ -4413,7 +4414,7 @@
         <v>1600</v>
       </c>
       <c r="C106" s="90">
-        <v>444.4975436146517</v>
+        <v>307.7554885329298</v>
       </c>
       <c r="D106" s="13"/>
       <c r="E106" s="13"/>
@@ -4425,7 +4426,7 @@
         <v>1800</v>
       </c>
       <c r="C107" s="90">
-        <v>471.53738499953806</v>
+        <v>370.57445368112303</v>
       </c>
       <c r="D107" s="13"/>
       <c r="E107" s="13"/>
@@ -4437,7 +4438,7 @@
         <v>2000</v>
       </c>
       <c r="C108" s="90">
-        <v>495.7215026372478</v>
+        <v>438.66544479602601</v>
       </c>
       <c r="D108" s="13"/>
       <c r="E108" s="13"/>
@@ -4449,7 +4450,7 @@
         <v>2200</v>
       </c>
       <c r="C109" s="90">
-        <v>517.85107736491</v>
+        <v>511.91508527943597</v>
       </c>
       <c r="D109" s="13"/>
       <c r="E109" s="13"/>
@@ -4461,7 +4462,7 @@
         <v>2400</v>
       </c>
       <c r="C110" s="92">
-        <v>538.47670431146423</v>
+        <v>590.20036286422874</v>
       </c>
       <c r="D110" s="13"/>
       <c r="E110" s="13"/>
@@ -4496,6 +4497,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010094F1BE91CAA32A4FA328597B4EFE3ACE" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2aca6f94c8d86978e70ae67b520b84e8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="39c0dabe-6791-4282-927d-9f4490665562" xmlns:ns3="806083ee-ebb1-4caa-b9ed-1b2719206aaa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3da35c08f3c516271253674fd62704d4" ns2:_="" ns3:_="">
     <xsd:import namespace="39c0dabe-6791-4282-927d-9f4490665562"/>
@@ -4730,15 +4740,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC3A9434-1DD4-4E97-96EB-F40ECFBA7CA0}">
   <ds:schemaRefs>
@@ -4751,6 +4752,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4189B351-766F-4F69-B90B-B94C56907ECD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499D88EC-070D-4C20-A0B5-20CB874A3D7D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4767,12 +4776,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4189B351-766F-4F69-B90B-B94C56907ECD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>